--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_335_R34.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_335_R34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3099</v>
+        <v>7.427</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3864</v>
+        <v>4.0075</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9236</v>
+        <v>3.4195</v>
       </c>
       <c r="G2" t="n">
         <v>3.6677</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5547</v>
+        <v>1.6718</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1221</v>
+        <v>0.7433</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4326</v>
+        <v>0.9285</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1638</v>
+        <v>5.7837</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2625</v>
+        <v>4.4119</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9013</v>
+        <v>1.3718</v>
       </c>
       <c r="G3" t="n">
         <v>3.7673</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2091</v>
+        <v>0.4107</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3462</v>
+        <v>0.4955</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5553</v>
+        <v>-0.0848</v>
       </c>
       <c r="V3" t="n">
         <v>0.6778999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8618</v>
+        <v>3.7831</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5585</v>
+        <v>2.3789</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3033</v>
+        <v>1.4042</v>
       </c>
       <c r="G4" t="n">
         <v>-0.8531</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>2.269</v>
+        <v>1.1903</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1429</v>
+        <v>0.9634</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1261</v>
+        <v>0.2269</v>
       </c>
       <c r="V4" t="n">
         <v>2.2862</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5572</v>
+        <v>2.6416</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0447</v>
+        <v>1.1715</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4876</v>
+        <v>1.4701</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.7559</v>
+        <v>2.2151</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8764</v>
+        <v>-2.7202</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1206</v>
+        <v>4.9353</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9374</v>
+        <v>1.9154</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.7471</v>
+        <v>-1.9725</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8097</v>
+        <v>3.8879</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8185</v>
+        <v>0.2997</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1294</v>
+        <v>-0.7477</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6891</v>
+        <v>1.0474</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6172</v>
+        <v>0.8905</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8377</v>
+        <v>0.5034</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2205</v>
+        <v>0.387</v>
       </c>
       <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.0722</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.1444</v>
       </c>
       <c r="X5" t="n">
         <v>-1.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5561</v>
+        <v>2.3042</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1532</v>
+        <v>2.7918</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4029</v>
+        <v>-0.4876</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2151</v>
+        <v>-1.7559</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.7202</v>
+        <v>-1.8764</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9353</v>
+        <v>0.1206</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9154</v>
+        <v>-0.9374</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.9725</v>
+        <v>-1.7471</v>
       </c>
       <c r="L6" t="n">
-        <v>3.8879</v>
+        <v>0.8097</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2997</v>
+        <v>-0.8185</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7477</v>
+        <v>-0.1294</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0474</v>
+        <v>-0.6891</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.195</v>
+        <v>1.3642</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5149</v>
+        <v>1.5848</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3198</v>
+        <v>-0.2205</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X6" t="n">
         <v>-1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1488</v>
+        <v>1.6506</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2943</v>
+        <v>1.6232</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4431</v>
+        <v>0.0274</v>
       </c>
       <c r="G7" t="n">
         <v>0.2355</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6008</v>
+        <v>0.1986</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.731</v>
+        <v>0.5979</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8698</v>
+        <v>-0.3993</v>
       </c>
       <c r="V7" t="n">
         <v>2.1444</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9827</v>
+        <v>-1.279</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7518</v>
+        <v>-1.1489</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2309</v>
+        <v>-0.13</v>
       </c>
       <c r="G8" t="n">
         <v>-3.0967</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3976</v>
+        <v>0.1013</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1404</v>
+        <v>0.7433</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7429</v>
+        <v>-0.642</v>
       </c>
       <c r="V8" t="n">
         <v>0.7886</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8843</v>
+        <v>-1.5394</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4179</v>
+        <v>-2.8714</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5336</v>
+        <v>1.332</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1745</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1485</v>
+        <v>0.4933</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3655</v>
+        <v>0.181</v>
       </c>
       <c r="U9" t="n">
-        <v>0.514</v>
+        <v>0.3123</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9304</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0979</v>
+        <v>-1.6612</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8015</v>
+        <v>-1.0624</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2963</v>
+        <v>-0.5988</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6969</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4731</v>
+        <v>-0.0365</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5816</v>
+        <v>0.1575</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1085</v>
+        <v>-0.1939</v>
       </c>
       <c r="V10" t="n">
         <v>0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4459</v>
+        <v>-2.1929</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3223</v>
+        <v>-0.9684</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1237</v>
+        <v>-1.2245</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2937</v>
@@ -1312,13 +1312,13 @@
         <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2245</v>
+        <v>0.0286</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2161</v>
+        <v>0.1377</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0083</v>
+        <v>-0.1092</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0547</v>
+        <v>-2.9629</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8315</v>
+        <v>-3.6388</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7768</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0004</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>0.554</v>
+        <v>0.6458</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3462</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2078</v>
+        <v>0.107</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.8345</v>
+        <v>13.9548</v>
       </c>
       <c r="E13" t="n">
-        <v>5.574599999999997</v>
+        <v>6.694899999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>7.2599</v>
+        <v>7.26</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9856</v>
@@ -1444,7 +1444,7 @@
         <v>2.019300000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-6.160699999999999</v>
+        <v>-6.1607</v>
       </c>
       <c r="L13" t="n">
         <v>8.179999999999998</v>
@@ -1468,10 +1468,10 @@
         <v>13.9173</v>
       </c>
       <c r="S13" t="n">
-        <v>5.838500000000002</v>
+        <v>6.9586</v>
       </c>
       <c r="T13" t="n">
-        <v>5.5264</v>
+        <v>6.646599999999999</v>
       </c>
       <c r="U13" t="n">
         <v>0.312</v>
@@ -1480,7 +1480,7 @@
         <v>5.502800000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>8.466900000000001</v>
+        <v>8.466899999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-2.9641</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.3042</v>
+        <v>8.838900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>7.03</v>
+        <v>7.6198</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2742</v>
+        <v>1.2191</v>
       </c>
       <c r="G14" t="n">
         <v>7.1601</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4615</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3443</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1173</v>
+        <v>-0.1724</v>
       </c>
       <c r="V14" t="n">
         <v>1.214</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.946</v>
+        <v>0.9961</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0696</v>
+        <v>1.5363</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1236</v>
+        <v>-0.5402</v>
       </c>
       <c r="G15" t="n">
         <v>-0.041</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3117</v>
+        <v>0.3618</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4732</v>
+        <v>0.9399</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1615</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2525</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0849</v>
+        <v>0.2428</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4051</v>
+        <v>0.641</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3202</v>
+        <v>-0.3982</v>
       </c>
       <c r="G16" t="n">
         <v>0.8686</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1059</v>
+        <v>0.0521</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.224</v>
+        <v>0.0119</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1182</v>
+        <v>0.0402</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6778999999999999</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6117</v>
+        <v>-0.7639</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1832</v>
+        <v>-2.0089</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5715</v>
+        <v>1.245</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0044</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0738</v>
+        <v>-0.226</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0227</v>
+        <v>0.197</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0965</v>
+        <v>-0.423</v>
       </c>
       <c r="V17" t="n">
         <v>0.3943</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.398</v>
+        <v>-1.1285</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2013</v>
+        <v>-0.9654</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1967</v>
+        <v>-0.1631</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1756</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5988</v>
+        <v>-0.3293</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1494</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4494</v>
+        <v>-0.4158</v>
       </c>
       <c r="V18" t="n">
         <v>1.0722</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7924</v>
+        <v>-1.3378</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9871</v>
+        <v>-1.6332</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1946</v>
+        <v>0.2954</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7929</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4635</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2908</v>
+        <v>0.063</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1726</v>
+        <v>-0.0718</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6078</v>
+        <v>-1.9286</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9498</v>
+        <v>-0.5959</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6581</v>
+        <v>-1.3327</v>
       </c>
       <c r="G20" t="n">
         <v>0.1951</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5863</v>
+        <v>-0.9072</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.963</v>
+        <v>-0.6091</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6234</v>
+        <v>-0.2981</v>
       </c>
       <c r="V20" t="n">
         <v>-2.1444</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. CORDINIER</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1778</v>
+        <v>-3.4835</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5502</v>
+        <v>-4.1478</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6277</v>
+        <v>0.6643</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3614</v>
+        <v>-0.6038</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5964</v>
+        <v>0.293</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.9578</v>
+        <v>-0.8968</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7391</v>
+        <v>-0.7397</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7968</v>
+        <v>-0.8466</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5359</v>
+        <v>0.1069</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6223</v>
+        <v>0.1359</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2004</v>
+        <v>1.1396</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.422</v>
+        <v>-1.0037</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6959</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2983</v>
+        <v>0.2801</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1889</v>
+        <v>0.0712</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4872</v>
+        <v>0.2089</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>I. CORDINIER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7657</v>
+        <v>-3.5488</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6196</v>
+        <v>-1.022</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8539</v>
+        <v>-2.5268</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6038</v>
+        <v>-2.3614</v>
       </c>
       <c r="H22" t="n">
-        <v>0.293</v>
+        <v>0.5964</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8968</v>
+        <v>-2.9578</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7397</v>
+        <v>-0.7391</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8466</v>
+        <v>0.7968</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1069</v>
+        <v>-1.5359</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1359</v>
+        <v>-1.6223</v>
       </c>
       <c r="N22" t="n">
-        <v>1.1396</v>
+        <v>-0.2004</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0037</v>
+        <v>-1.422</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0022</v>
+        <v>-0.6693</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4007</v>
+        <v>-0.2829</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3985</v>
+        <v>-0.3864</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. SMITS</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2546</v>
+        <v>-3.8939</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5343</v>
+        <v>-3.0721</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.8218</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7010999999999999</v>
+        <v>0.442</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1056</v>
+        <v>2.8679</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5955</v>
+        <v>-2.426</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1614</v>
+        <v>-0.6193</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1982</v>
+        <v>1.4354</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0368</v>
+        <v>-2.0547</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5397999999999999</v>
+        <v>1.0612</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0926</v>
+        <v>1.4325</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6323</v>
+        <v>-0.3713</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.0154</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.7112</v>
+        <v>-2.5515</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5381</v>
+        <v>-0.3539</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3383</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8764</v>
+        <v>-0.4525</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.8223</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>R. SMITS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5617</v>
+        <v>-4.4683</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1337</v>
+        <v>-4.0061</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4281</v>
+        <v>-0.4622</v>
       </c>
       <c r="G24" t="n">
-        <v>0.442</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>2.8679</v>
+        <v>-0.1056</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.426</v>
+        <v>-0.5955</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6193</v>
+        <v>-0.1614</v>
       </c>
       <c r="K24" t="n">
-        <v>1.4354</v>
+        <v>-0.1982</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.0547</v>
+        <v>0.0368</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0612</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>1.4325</v>
+        <v>0.0926</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3713</v>
+        <v>-0.6323</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1598</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.5515</v>
+        <v>-3.7112</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.0217</v>
+        <v>-0.7519</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.963</v>
+        <v>-0.1336</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0587</v>
+        <v>-0.6183</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.8223</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.8223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.8346</v>
+        <v>-10.4755</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.6545</v>
+        <v>-7.654300000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.1805</v>
+        <v>-2.8212</v>
       </c>
       <c r="G25" t="n">
         <v>1.9856</v>
       </c>
       <c r="H25" t="n">
-        <v>9.597800000000001</v>
+        <v>9.597799999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-7.612200000000001</v>
@@ -2395,7 +2395,7 @@
         <v>-8.18</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.479400000000001</v>
+        <v>-3.4794</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.9172</v>
@@ -2404,13 +2404,13 @@
         <v>10.438</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.8384</v>
+        <v>-3.4793</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3121000000000004</v>
+        <v>-0.3119999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.5263</v>
+        <v>-3.1673</v>
       </c>
       <c r="V25" t="n">
         <v>-5.5028</v>
